--- a/branches/release/v2027.0.0-ballot/StructureDefinition-mii-ex-bildgebung-modalitaet-us.xlsx
+++ b/branches/release/v2027.0.0-ballot/StructureDefinition-mii-ex-bildgebung-modalitaet-us.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T09:21:34+00:00</t>
+    <t>2026-09-14T10:46:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/release/v2027.0.0-ballot/StructureDefinition-mii-ex-bildgebung-modalitaet-us.xlsx
+++ b/branches/release/v2027.0.0-ballot/StructureDefinition-mii-ex-bildgebung-modalitaet-us.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T10:46:28+00:00</t>
+    <t>2026-09-14T12:46:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/release/v2027.0.0-ballot/StructureDefinition-mii-ex-bildgebung-modalitaet-us.xlsx
+++ b/branches/release/v2027.0.0-ballot/StructureDefinition-mii-ex-bildgebung-modalitaet-us.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T12:46:28+00:00</t>
+    <t>2026-09-14T13:01:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/release/v2027.0.0-ballot/StructureDefinition-mii-ex-bildgebung-modalitaet-us.xlsx
+++ b/branches/release/v2027.0.0-ballot/StructureDefinition-mii-ex-bildgebung-modalitaet-us.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T13:01:34+00:00</t>
+    <t>2026-09-14T13:19:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/release/v2027.0.0-ballot/StructureDefinition-mii-ex-bildgebung-modalitaet-us.xlsx
+++ b/branches/release/v2027.0.0-ballot/StructureDefinition-mii-ex-bildgebung-modalitaet-us.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T13:19:56+00:00</t>
+    <t>2026-09-14T13:46:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/release/v2027.0.0-ballot/StructureDefinition-mii-ex-bildgebung-modalitaet-us.xlsx
+++ b/branches/release/v2027.0.0-ballot/StructureDefinition-mii-ex-bildgebung-modalitaet-us.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T13:46:54+00:00</t>
+    <t>2026-09-14T14:28:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/release/v2027.0.0-ballot/StructureDefinition-mii-ex-bildgebung-modalitaet-us.xlsx
+++ b/branches/release/v2027.0.0-ballot/StructureDefinition-mii-ex-bildgebung-modalitaet-us.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T14:28:48+00:00</t>
+    <t>2026-09-14T19:58:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
